--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.007900000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="E2">
-        <v>-0.0408</v>
+        <v>-0.11</v>
       </c>
       <c r="G2">
-        <v>0.1098279257215051</v>
+        <v>0.03061359776590394</v>
       </c>
       <c r="H2">
-        <v>0.1098279257215051</v>
+        <v>0.03061359776590394</v>
       </c>
       <c r="I2">
-        <v>0.06043950226915015</v>
+        <v>-0.03909457659291933</v>
       </c>
       <c r="J2">
-        <v>0.04501490074900365</v>
+        <v>-0.03047148344929136</v>
       </c>
       <c r="K2">
-        <v>2225.5</v>
+        <v>1442.1</v>
       </c>
       <c r="L2">
-        <v>0.03926900192683667</v>
+        <v>0.03034843564873175</v>
       </c>
       <c r="M2">
-        <v>676.5295</v>
+        <v>390.5138</v>
       </c>
       <c r="N2">
-        <v>0.05275289484970174</v>
+        <v>0.030922233923778</v>
       </c>
       <c r="O2">
-        <v>0.3039898899123792</v>
+        <v>0.2707952291796686</v>
       </c>
       <c r="P2">
-        <v>410.6295</v>
+        <v>389.0838</v>
       </c>
       <c r="Q2">
-        <v>0.03201914304651254</v>
+        <v>0.03080900157575086</v>
       </c>
       <c r="R2">
-        <v>0.1845111210963828</v>
+        <v>0.2698036197212399</v>
       </c>
       <c r="S2">
-        <v>265.9</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>0.3930353369660894</v>
+        <v>0.003661842424006526</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="V2">
-        <v>0.0001317790167257983</v>
+        <v>0.0001259017016525588</v>
       </c>
       <c r="W2">
-        <v>0.04762953807746281</v>
+        <v>0.05054178564615179</v>
       </c>
       <c r="X2">
-        <v>0.1058462369190762</v>
+        <v>0.1500556067598406</v>
       </c>
       <c r="Y2">
-        <v>-0.05821669884161343</v>
+        <v>-0.0995138211136888</v>
       </c>
       <c r="Z2">
-        <v>0.8594833866859329</v>
+        <v>0.6876644248662569</v>
       </c>
       <c r="AA2">
-        <v>0.04256781656984977</v>
+        <v>-0.02767387689789078</v>
       </c>
       <c r="AB2">
-        <v>0.05793720027595455</v>
+        <v>0.08652767011806681</v>
       </c>
       <c r="AC2">
-        <v>-0.01468213431145585</v>
+        <v>-0.113693356018718</v>
       </c>
       <c r="AD2">
-        <v>23935</v>
+        <v>23719.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23935</v>
+        <v>23719.8</v>
       </c>
       <c r="AG2">
-        <v>23933.31</v>
+        <v>23718.21</v>
       </c>
       <c r="AH2">
-        <v>0.6511241991866048</v>
+        <v>0.652562540063331</v>
       </c>
       <c r="AI2">
-        <v>0.3300673649081921</v>
+        <v>0.5079708406859806</v>
       </c>
       <c r="AJ2">
-        <v>0.6511081590551777</v>
+        <v>0.6525473414530069</v>
       </c>
       <c r="AK2">
-        <v>0.3300517515215378</v>
+        <v>0.5079540862229328</v>
       </c>
       <c r="AL2">
-        <v>452.7</v>
+        <v>462.8</v>
       </c>
       <c r="AM2">
-        <v>452.7</v>
+        <v>462.8</v>
       </c>
       <c r="AN2">
-        <v>5.808902048344821</v>
+        <v>-16.23309608540925</v>
       </c>
       <c r="AO2">
-        <v>7.566379500773139</v>
+        <v>-4.014044943820225</v>
       </c>
       <c r="AP2">
-        <v>5.808491893990875</v>
+        <v>-16.23200793868054</v>
       </c>
       <c r="AQ2">
-        <v>7.566379500773139</v>
+        <v>-4.014044943820225</v>
       </c>
     </row>
     <row r="3">
@@ -722,50 +722,50 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0191</v>
-      </c>
-      <c r="E3">
-        <v>0.0447</v>
+        <v>-0.0074</v>
       </c>
       <c r="G3">
-        <v>0.1567706980368872</v>
+        <v>0.09592044298790824</v>
       </c>
       <c r="H3">
-        <v>0.1567706980368872</v>
+        <v>0.09592044298790824</v>
       </c>
       <c r="I3">
-        <v>0.1299402530893977</v>
+        <v>0.05758842807096847</v>
       </c>
       <c r="J3">
-        <v>0.09983320989541369</v>
+        <v>0.04359843718997485</v>
       </c>
       <c r="K3">
-        <v>228.8</v>
+        <v>117.8</v>
       </c>
       <c r="L3">
-        <v>0.04245370542175382</v>
+        <v>0.02662447734207255</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>67.3488</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1123978638184246</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.5717215619694397</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>67.3488</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1123978638184246</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.5717215619694397</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -773,67 +773,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.08643421102338408</v>
+        <v>0.04570320077594568</v>
       </c>
       <c r="X3">
-        <v>0.06974407650636584</v>
+        <v>0.107304412454364</v>
       </c>
       <c r="Y3">
-        <v>0.01669013451701824</v>
+        <v>-0.06160121167841834</v>
       </c>
       <c r="Z3">
-        <v>1.855342880749105</v>
+        <v>1.562709709320807</v>
       </c>
       <c r="AA3">
-        <v>0.1852248352417869</v>
+        <v>0.06813170110798704</v>
       </c>
       <c r="AB3">
-        <v>0.05990908768798406</v>
+        <v>0.08990698436926335</v>
       </c>
       <c r="AC3">
-        <v>0.1253157475538028</v>
+        <v>-0.02177528326127631</v>
       </c>
       <c r="AD3">
-        <v>253.8</v>
+        <v>208.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>253.8</v>
+        <v>208.9</v>
       </c>
       <c r="AG3">
-        <v>253.8</v>
+        <v>208.9</v>
       </c>
       <c r="AH3">
-        <v>0.2270328294122909</v>
+        <v>0.258507610444252</v>
       </c>
       <c r="AI3">
-        <v>0.08964080104545614</v>
+        <v>0.140844120819849</v>
       </c>
       <c r="AJ3">
-        <v>0.2270328294122909</v>
+        <v>0.258507610444252</v>
       </c>
       <c r="AK3">
-        <v>0.08964080104545614</v>
+        <v>0.140844120819849</v>
       </c>
       <c r="AL3">
-        <v>12.1</v>
+        <v>9.9</v>
       </c>
       <c r="AM3">
-        <v>12.1</v>
+        <v>9.9</v>
       </c>
       <c r="AN3">
-        <v>0.3530393656975936</v>
+        <v>0.7731310140636566</v>
       </c>
       <c r="AO3">
-        <v>57.87603305785124</v>
+        <v>25.73737373737374</v>
       </c>
       <c r="AP3">
-        <v>0.3530393656975936</v>
+        <v>0.7731310140636566</v>
       </c>
       <c r="AQ3">
-        <v>57.87603305785124</v>
+        <v>25.73737373737374</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mirae Asset Life Insurance Co., Ltd. (KOSE:A085620)</t>
+          <t>Samsung Life Insurance Co., Ltd. (KOSE:A032830)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,121 +853,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0392</v>
+        <v>0.01</v>
       </c>
       <c r="E4">
-        <v>-0.233</v>
+        <v>-0.11</v>
       </c>
       <c r="G4">
-        <v>0.1397738573164893</v>
+        <v>0.03719569579345491</v>
       </c>
       <c r="H4">
-        <v>0.1397738573164893</v>
+        <v>0.03719569579345491</v>
       </c>
       <c r="I4">
-        <v>0.05016389819896136</v>
+        <v>-0.06037253404833354</v>
       </c>
       <c r="J4">
-        <v>0.03651931788884387</v>
+        <v>-0.04870111653426934</v>
       </c>
       <c r="K4">
-        <v>25.5</v>
+        <v>493.6</v>
       </c>
       <c r="L4">
-        <v>0.009391919266325367</v>
+        <v>0.02191167853401282</v>
       </c>
       <c r="M4">
-        <v>276.9924999999999</v>
+        <v>312.6</v>
       </c>
       <c r="N4">
-        <v>0.6311061745272271</v>
+        <v>0.03099622214950769</v>
       </c>
       <c r="O4">
-        <v>10.86245098039215</v>
+        <v>0.6333063209076175</v>
       </c>
       <c r="P4">
-        <v>11.0925</v>
+        <v>312.6</v>
       </c>
       <c r="Q4">
-        <v>0.02527341079972659</v>
+        <v>0.03099622214950769</v>
       </c>
       <c r="R4">
-        <v>0.4350000000000001</v>
+        <v>0.6333063209076175</v>
       </c>
       <c r="S4">
-        <v>265.9</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.959953789362528</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.0001576583276318529</v>
       </c>
       <c r="W4">
-        <v>0.01331175610774692</v>
+        <v>0.01561852326482826</v>
       </c>
       <c r="X4">
-        <v>0.09215596396302463</v>
+        <v>0.1595870604334305</v>
       </c>
       <c r="Y4">
-        <v>-0.07884420785527771</v>
+        <v>-0.1439685371686022</v>
       </c>
       <c r="Z4">
-        <v>1.251255818240472</v>
+        <v>0.4631845510840943</v>
       </c>
       <c r="AA4">
-        <v>0.04569500898658924</v>
+        <v>-0.0225576047992197</v>
       </c>
       <c r="AB4">
-        <v>0.05712604323464604</v>
+        <v>0.0854335366375524</v>
       </c>
       <c r="AC4">
-        <v>-0.0114310342480568</v>
+        <v>-0.1079911414367721</v>
       </c>
       <c r="AD4">
-        <v>421.8</v>
+        <v>16462</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>421.8</v>
+        <v>16462</v>
       </c>
       <c r="AG4">
-        <v>421.8</v>
+        <v>16460.41</v>
       </c>
       <c r="AH4">
-        <v>0.4900662251655629</v>
+        <v>0.6201053975763832</v>
       </c>
       <c r="AI4">
-        <v>0.2074460237053067</v>
+        <v>0.5165813124466536</v>
       </c>
       <c r="AJ4">
-        <v>0.4900662251655629</v>
+        <v>0.6200826429780403</v>
       </c>
       <c r="AK4">
-        <v>0.2074460237053067</v>
+        <v>0.5165571912792506</v>
       </c>
       <c r="AL4">
-        <v>12.7</v>
+        <v>437.7</v>
       </c>
       <c r="AM4">
-        <v>12.7</v>
+        <v>437.7</v>
       </c>
       <c r="AN4">
-        <v>2.368332397529478</v>
+        <v>-13.52226055528175</v>
       </c>
       <c r="AO4">
-        <v>10.7244094488189</v>
+        <v>-3.10715101667809</v>
       </c>
       <c r="AP4">
-        <v>2.368332397529478</v>
+        <v>-13.52095449318219</v>
       </c>
       <c r="AQ4">
-        <v>10.7244094488189</v>
+        <v>-3.10715101667809</v>
       </c>
     </row>
     <row r="5">
@@ -987,53 +987,50 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0545</v>
+        <v>0.048</v>
       </c>
       <c r="E5">
-        <v>-0.0255</v>
+        <v>0.134</v>
       </c>
       <c r="G5">
-        <v>0.08816551293191825</v>
+        <v>0.008229320123250932</v>
       </c>
       <c r="H5">
-        <v>0.08816551293191825</v>
+        <v>0.008229320123250932</v>
       </c>
       <c r="I5">
-        <v>0.0337479618437625</v>
+        <v>-0.03149266376347046</v>
       </c>
       <c r="J5">
-        <v>0.02382761133371016</v>
+        <v>-0.02760584689444132</v>
       </c>
       <c r="K5">
-        <v>647.6</v>
+        <v>746.4</v>
       </c>
       <c r="L5">
-        <v>0.03161461028500015</v>
+        <v>0.04027780026225899</v>
       </c>
       <c r="M5">
-        <v>18.785</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.01014035087719298</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.02900710315009265</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>18.785</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.01014035087719298</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.02900710315009265</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
@@ -1041,49 +1038,49 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.05443343335770902</v>
+        <v>0.07842725199903332</v>
       </c>
       <c r="X5">
-        <v>0.170184583621497</v>
+        <v>0.258899964847324</v>
       </c>
       <c r="Y5">
-        <v>-0.1157511502637879</v>
+        <v>-0.1804727128482906</v>
       </c>
       <c r="Z5">
-        <v>1.655248761646182</v>
+        <v>1.187797248964836</v>
       </c>
       <c r="AA5">
-        <v>0.03944062415311029</v>
+        <v>-0.03279014899656187</v>
       </c>
       <c r="AB5">
-        <v>0.0573738585279652</v>
+        <v>0.08660542160410203</v>
       </c>
       <c r="AC5">
-        <v>-0.01793323437485491</v>
+        <v>-0.1193955706006639</v>
       </c>
       <c r="AD5">
-        <v>6084.3</v>
+        <v>6701.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6084.3</v>
+        <v>6701.6</v>
       </c>
       <c r="AG5">
-        <v>6084.3</v>
+        <v>6701.6</v>
       </c>
       <c r="AH5">
-        <v>0.7665935893559117</v>
+        <v>0.8027887253081614</v>
       </c>
       <c r="AI5">
-        <v>0.3504397560174866</v>
+        <v>0.5548417008875347</v>
       </c>
       <c r="AJ5">
-        <v>0.7665935893559117</v>
+        <v>0.8027887253081614</v>
       </c>
       <c r="AK5">
-        <v>0.3504397560174866</v>
+        <v>0.5548417008875347</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1092,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>6.550710594315246</v>
+        <v>-17.75258278145695</v>
       </c>
       <c r="AP5">
-        <v>6.550710594315246</v>
+        <v>-17.75258278145695</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samsung Life Insurance Co., Ltd. (KOSE:A032830)</t>
+          <t>MIRAE ASSET Life Insurance Co., Ltd. (KOSE:A085620)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,121 +1112,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0349</v>
+        <v>-0.0382</v>
       </c>
       <c r="E6">
-        <v>-0.0561</v>
+        <v>-0.129</v>
       </c>
       <c r="G6">
-        <v>0.1137246523883281</v>
+        <v>0.01960206337509211</v>
       </c>
       <c r="H6">
-        <v>0.1137246523883281</v>
+        <v>0.01960206337509211</v>
       </c>
       <c r="I6">
-        <v>0.06756395876729157</v>
+        <v>-0.08297715549005159</v>
       </c>
       <c r="J6">
-        <v>0.05248530702523508</v>
+        <v>-0.05620817773340582</v>
       </c>
       <c r="K6">
-        <v>1323.6</v>
+        <v>84.3</v>
       </c>
       <c r="L6">
-        <v>0.04712919938044117</v>
+        <v>0.04141488577745026</v>
       </c>
       <c r="M6">
-        <v>380.752</v>
+        <v>10.565</v>
       </c>
       <c r="N6">
-        <v>0.03937863274382046</v>
+        <v>0.03541736506872276</v>
       </c>
       <c r="O6">
-        <v>0.2876639468117256</v>
+        <v>0.1253262158956109</v>
       </c>
       <c r="P6">
-        <v>380.752</v>
+        <v>9.135000000000002</v>
       </c>
       <c r="Q6">
-        <v>0.03937863274382046</v>
+        <v>0.0306235333556822</v>
       </c>
       <c r="R6">
-        <v>0.2876639468117256</v>
+        <v>0.1083629893238434</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.1353525792711784</v>
       </c>
       <c r="U6">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.0001747853966284</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.0408256427972166</v>
+        <v>0.0553803705163579</v>
       </c>
       <c r="X6">
-        <v>0.1195365098751278</v>
+        <v>0.1405241530862507</v>
       </c>
       <c r="Y6">
-        <v>-0.07871086707791125</v>
+        <v>-0.08514378256989279</v>
       </c>
       <c r="Z6">
-        <v>0.5791970414537991</v>
+        <v>1.001032753024491</v>
       </c>
       <c r="AA6">
-        <v>0.03039933454881046</v>
+        <v>-0.05626622689896112</v>
       </c>
       <c r="AB6">
-        <v>0.05850054202394391</v>
+        <v>0.08644991863203159</v>
       </c>
       <c r="AC6">
-        <v>-0.02810120747513345</v>
+        <v>-0.1427161455309927</v>
       </c>
       <c r="AD6">
-        <v>17175.1</v>
+        <v>347.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>17175.1</v>
+        <v>347.3</v>
       </c>
       <c r="AG6">
-        <v>17173.41</v>
+        <v>347.3</v>
       </c>
       <c r="AH6">
-        <v>0.6398091200673518</v>
+        <v>0.5379491945477075</v>
       </c>
       <c r="AI6">
-        <v>0.3415279683429776</v>
+        <v>0.2742419456727732</v>
       </c>
       <c r="AJ6">
-        <v>0.6397864424245066</v>
+        <v>0.5379491945477075</v>
       </c>
       <c r="AK6">
-        <v>0.341505839147093</v>
+        <v>0.2742419456727732</v>
       </c>
       <c r="AL6">
-        <v>427.9</v>
+        <v>15.2</v>
       </c>
       <c r="AM6">
-        <v>427.9</v>
+        <v>15.2</v>
       </c>
       <c r="AN6">
-        <v>7.485008280310294</v>
+        <v>-2.544322344322345</v>
       </c>
       <c r="AO6">
-        <v>4.434447300771208</v>
+        <v>-11.11184210526316</v>
       </c>
       <c r="AP6">
-        <v>7.484271768499957</v>
+        <v>-2.544322344322345</v>
       </c>
       <c r="AQ6">
-        <v>4.434447300771208</v>
+        <v>-11.11184210526316</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0013</v>
+        <v>0.035275</v>
       </c>
       <c r="E2">
-        <v>-0.11</v>
+        <v>0.10585</v>
+      </c>
+      <c r="F2">
+        <v>0.102</v>
       </c>
       <c r="G2">
-        <v>0.03061359776590394</v>
+        <v>0.06105130221973214</v>
       </c>
       <c r="H2">
-        <v>0.03061359776590394</v>
+        <v>0.06105130221973214</v>
       </c>
       <c r="I2">
-        <v>-0.03909457659291933</v>
+        <v>0.01902731823582122</v>
       </c>
       <c r="J2">
-        <v>-0.03047148344929136</v>
+        <v>0.01749548871412529</v>
       </c>
       <c r="K2">
-        <v>1442.1</v>
+        <v>2001.9</v>
       </c>
       <c r="L2">
-        <v>0.03034843564873175</v>
+        <v>0.03653442199912766</v>
       </c>
       <c r="M2">
-        <v>390.5138</v>
+        <v>400.508</v>
       </c>
       <c r="N2">
-        <v>0.030922233923778</v>
+        <v>0.03249425986775385</v>
       </c>
       <c r="O2">
-        <v>0.2707952291796686</v>
+        <v>0.2000639392577052</v>
       </c>
       <c r="P2">
-        <v>389.0838</v>
+        <v>400.508</v>
       </c>
       <c r="Q2">
-        <v>0.03080900157575086</v>
+        <v>0.03249425986775385</v>
       </c>
       <c r="R2">
-        <v>0.2698036197212399</v>
+        <v>0.2000639392577052</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.003661842424006526</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="V2">
-        <v>0.0001259017016525588</v>
+        <v>0.0001711898097440266</v>
       </c>
       <c r="W2">
-        <v>0.05054178564615179</v>
+        <v>0.0896642226042354</v>
       </c>
       <c r="X2">
-        <v>0.1500556067598406</v>
+        <v>0.1209033755528086</v>
       </c>
       <c r="Y2">
-        <v>-0.0995138211136888</v>
+        <v>-0.03123915294857321</v>
       </c>
       <c r="Z2">
-        <v>0.6876644248662569</v>
+        <v>1.237424463222829</v>
       </c>
       <c r="AA2">
-        <v>-0.02767387689789078</v>
+        <v>0.05561058891811879</v>
       </c>
       <c r="AB2">
-        <v>0.08652767011806681</v>
+        <v>0.07447550749894481</v>
       </c>
       <c r="AC2">
-        <v>-0.113693356018718</v>
+        <v>-0.01764489664558282</v>
       </c>
       <c r="AD2">
-        <v>23719.8</v>
+        <v>26123.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23719.8</v>
+        <v>26123.2</v>
       </c>
       <c r="AG2">
-        <v>23718.21</v>
+        <v>26121.09</v>
       </c>
       <c r="AH2">
-        <v>0.652562540063331</v>
+        <v>0.6794299937319078</v>
       </c>
       <c r="AI2">
-        <v>0.5079708406859806</v>
+        <v>0.3415435826566273</v>
       </c>
       <c r="AJ2">
-        <v>0.6525473414530069</v>
+        <v>0.6794124004235487</v>
       </c>
       <c r="AK2">
-        <v>0.5079540862229328</v>
+        <v>0.3415254174130686</v>
       </c>
       <c r="AL2">
-        <v>462.8</v>
+        <v>932.1</v>
       </c>
       <c r="AM2">
-        <v>462.8</v>
+        <v>932.1</v>
       </c>
       <c r="AN2">
-        <v>-16.23309608540925</v>
+        <v>16.39771514656958</v>
       </c>
       <c r="AO2">
-        <v>-4.014044943820225</v>
+        <v>1.118549511854951</v>
       </c>
       <c r="AP2">
-        <v>-16.23200793868054</v>
+        <v>16.39639068482832</v>
       </c>
       <c r="AQ2">
-        <v>-4.014044943820225</v>
+        <v>1.118549511854951</v>
       </c>
     </row>
     <row r="3">
@@ -722,50 +725,50 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0074</v>
+        <v>0.12</v>
+      </c>
+      <c r="E3">
+        <v>0.154</v>
       </c>
       <c r="G3">
-        <v>0.09592044298790824</v>
+        <v>0.07073361738276325</v>
       </c>
       <c r="H3">
-        <v>0.09592044298790824</v>
+        <v>0.07073361738276325</v>
       </c>
       <c r="I3">
-        <v>0.05758842807096847</v>
+        <v>0.1387063804935027</v>
       </c>
       <c r="J3">
-        <v>0.04359843718997485</v>
+        <v>0.1124059126340587</v>
       </c>
       <c r="K3">
-        <v>117.8</v>
+        <v>98.3</v>
       </c>
       <c r="L3">
-        <v>0.02662447734207255</v>
+        <v>0.01304769110288164</v>
       </c>
       <c r="M3">
-        <v>67.3488</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1123978638184246</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5717215619694397</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>67.3488</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1123978638184246</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5717215619694397</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -773,67 +776,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.04570320077594568</v>
+        <v>0.0771403908027937</v>
       </c>
       <c r="X3">
-        <v>0.107304412454364</v>
+        <v>0.08862582417263795</v>
       </c>
       <c r="Y3">
-        <v>-0.06160121167841834</v>
+        <v>-0.01148543336984426</v>
       </c>
       <c r="Z3">
-        <v>1.562709709320807</v>
+        <v>5.079490291262135</v>
       </c>
       <c r="AA3">
-        <v>0.06813170110798704</v>
+        <v>0.5709647419051608</v>
       </c>
       <c r="AB3">
-        <v>0.08990698436926335</v>
+        <v>0.07781499524640231</v>
       </c>
       <c r="AC3">
-        <v>-0.02177528326127631</v>
+        <v>0.4931497466587584</v>
       </c>
       <c r="AD3">
-        <v>208.9</v>
+        <v>148.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>208.9</v>
+        <v>148.3</v>
       </c>
       <c r="AG3">
-        <v>208.9</v>
+        <v>148.3</v>
       </c>
       <c r="AH3">
-        <v>0.258507610444252</v>
+        <v>0.2127690100430416</v>
       </c>
       <c r="AI3">
-        <v>0.140844120819849</v>
+        <v>0.05824594477828836</v>
       </c>
       <c r="AJ3">
-        <v>0.258507610444252</v>
+        <v>0.2127690100430416</v>
       </c>
       <c r="AK3">
-        <v>0.140844120819849</v>
+        <v>0.05824594477828836</v>
       </c>
       <c r="AL3">
-        <v>9.9</v>
+        <v>46.5</v>
       </c>
       <c r="AM3">
-        <v>9.9</v>
+        <v>46.5</v>
       </c>
       <c r="AN3">
-        <v>0.7731310140636566</v>
+        <v>0.1396158915458482</v>
       </c>
       <c r="AO3">
-        <v>25.73737373737374</v>
+        <v>22.47311827956989</v>
       </c>
       <c r="AP3">
-        <v>0.7731310140636566</v>
+        <v>0.1396158915458482</v>
       </c>
       <c r="AQ3">
-        <v>25.73737373737374</v>
+        <v>22.47311827956989</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samsung Life Insurance Co., Ltd. (KOSE:A032830)</t>
+          <t>Hanwha Life Insurance Co., Ltd. (KOSE:A088350)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,121 +856,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.01</v>
+        <v>0.0614</v>
       </c>
       <c r="E4">
-        <v>-0.11</v>
+        <v>-0.0294</v>
       </c>
       <c r="G4">
-        <v>0.03719569579345491</v>
+        <v>0.05474449295938139</v>
       </c>
       <c r="H4">
-        <v>0.03719569579345491</v>
+        <v>0.05474449295938139</v>
       </c>
       <c r="I4">
-        <v>-0.06037253404833354</v>
+        <v>0.04313216004571715</v>
       </c>
       <c r="J4">
-        <v>-0.04870111653426934</v>
+        <v>0.04313216004571715</v>
       </c>
       <c r="K4">
-        <v>493.6</v>
+        <v>187.7</v>
       </c>
       <c r="L4">
-        <v>0.02191167853401282</v>
+        <v>0.00837998803496647</v>
       </c>
       <c r="M4">
-        <v>312.6</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03099622214950769</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6333063209076175</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>312.6</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03099622214950769</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6333063209076175</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.0001576583276318529</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.01561852326482826</v>
+        <v>0.04272803842564138</v>
       </c>
       <c r="X4">
-        <v>0.1595870604334305</v>
+        <v>0.226107129230268</v>
       </c>
       <c r="Y4">
-        <v>-0.1439685371686022</v>
+        <v>-0.1833790908046266</v>
       </c>
       <c r="Z4">
-        <v>0.4631845510840943</v>
+        <v>2.018892243904638</v>
       </c>
       <c r="AA4">
-        <v>-0.0225576047992197</v>
+        <v>0.08707918337915184</v>
       </c>
       <c r="AB4">
-        <v>0.0854335366375524</v>
+        <v>0.07364633245079008</v>
       </c>
       <c r="AC4">
-        <v>-0.1079911414367721</v>
+        <v>0.01343285092836176</v>
       </c>
       <c r="AD4">
-        <v>16462</v>
+        <v>7757.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>16462</v>
+        <v>7757.1</v>
       </c>
       <c r="AG4">
-        <v>16460.41</v>
+        <v>7757.1</v>
       </c>
       <c r="AH4">
-        <v>0.6201053975763832</v>
+        <v>0.8244077667839265</v>
       </c>
       <c r="AI4">
-        <v>0.5165813124466536</v>
+        <v>0.3820102432778489</v>
       </c>
       <c r="AJ4">
-        <v>0.6200826429780403</v>
+        <v>0.8244077667839265</v>
       </c>
       <c r="AK4">
-        <v>0.5165571912792506</v>
+        <v>0.3820102432778489</v>
       </c>
       <c r="AL4">
-        <v>437.7</v>
+        <v>129.1</v>
       </c>
       <c r="AM4">
-        <v>437.7</v>
+        <v>129.1</v>
       </c>
       <c r="AN4">
-        <v>-13.52226055528175</v>
+        <v>6.672774193548388</v>
       </c>
       <c r="AO4">
-        <v>-3.10715101667809</v>
+        <v>7.483346243222309</v>
       </c>
       <c r="AP4">
-        <v>-13.52095449318219</v>
+        <v>6.672774193548388</v>
       </c>
       <c r="AQ4">
-        <v>-3.10715101667809</v>
+        <v>7.483346243222309</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hanwha Life Insurance Co., Ltd. (KOSE:A088350)</t>
+          <t>Samsung Life Insurance Co., Ltd. (KOSE:A032830)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,112 +987,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.048</v>
+        <v>0.00915</v>
       </c>
       <c r="E5">
-        <v>0.134</v>
+        <v>0.0617</v>
+      </c>
+      <c r="F5">
+        <v>0.102</v>
       </c>
       <c r="G5">
-        <v>0.008229320123250932</v>
+        <v>0.06427264977778514</v>
       </c>
       <c r="H5">
-        <v>0.008229320123250932</v>
+        <v>0.06427264977778514</v>
       </c>
       <c r="I5">
-        <v>-0.03149266376347046</v>
+        <v>0.03139560867010403</v>
       </c>
       <c r="J5">
-        <v>-0.02760584689444132</v>
+        <v>0.03040732644102825</v>
       </c>
       <c r="K5">
-        <v>746.4</v>
+        <v>1629.5</v>
       </c>
       <c r="L5">
-        <v>0.04027780026225899</v>
+        <v>0.06743000438636421</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>400.508</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.0415400093346471</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.2457858238723535</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>400.508</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.0415400093346471</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.2457858238723535</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.0002188456153088212</v>
       </c>
       <c r="W5">
-        <v>0.07842725199903332</v>
+        <v>0.1156157541098758</v>
       </c>
       <c r="X5">
-        <v>0.258899964847324</v>
+        <v>0.1377431515796403</v>
       </c>
       <c r="Y5">
-        <v>-0.1804727128482906</v>
+        <v>-0.02212739746976458</v>
       </c>
       <c r="Z5">
-        <v>1.187797248964836</v>
+        <v>0.7939532107140874</v>
       </c>
       <c r="AA5">
-        <v>-0.03279014899656187</v>
+        <v>0.02414199445708574</v>
       </c>
       <c r="AB5">
-        <v>0.08660542160410203</v>
+        <v>0.07286463867661315</v>
       </c>
       <c r="AC5">
-        <v>-0.1193955706006639</v>
+        <v>-0.04872264421952741</v>
       </c>
       <c r="AD5">
-        <v>6701.6</v>
+        <v>17847.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6701.6</v>
+        <v>17847.2</v>
       </c>
       <c r="AG5">
-        <v>6701.6</v>
+        <v>17845.09</v>
       </c>
       <c r="AH5">
-        <v>0.8027887253081614</v>
+        <v>0.6492558760508864</v>
       </c>
       <c r="AI5">
-        <v>0.5548417008875347</v>
+        <v>0.3497763823724243</v>
       </c>
       <c r="AJ5">
-        <v>0.8027887253081614</v>
+        <v>0.649228951281334</v>
       </c>
       <c r="AK5">
-        <v>0.5548417008875347</v>
+        <v>0.3497494928216949</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>739.9</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>739.9</v>
       </c>
       <c r="AN5">
-        <v>-17.75258278145695</v>
+        <v>16.78788448875929</v>
+      </c>
+      <c r="AO5">
+        <v>1.025408839032302</v>
       </c>
       <c r="AP5">
-        <v>-17.75258278145695</v>
+        <v>16.78589972721287</v>
+      </c>
+      <c r="AQ5">
+        <v>1.025408839032302</v>
       </c>
     </row>
     <row r="6">
@@ -1112,52 +1124,49 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0382</v>
+        <v>-0.238</v>
       </c>
       <c r="E6">
-        <v>-0.129</v>
+        <v>0.15</v>
       </c>
       <c r="G6">
-        <v>0.01960206337509211</v>
+        <v>0.04737295434969854</v>
       </c>
       <c r="H6">
-        <v>0.01960206337509211</v>
+        <v>0.04737295434969854</v>
       </c>
       <c r="I6">
-        <v>-0.08297715549005159</v>
+        <v>-2.479471719781797</v>
       </c>
       <c r="J6">
-        <v>-0.05620817773340582</v>
+        <v>-2.229202461905799</v>
       </c>
       <c r="K6">
-        <v>84.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L6">
-        <v>0.04141488577745026</v>
+        <v>0.124031007751938</v>
       </c>
       <c r="M6">
-        <v>10.565</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03541736506872276</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1253262158956109</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>9.135000000000002</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.0306235333556822</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1083629893238434</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
-      </c>
-      <c r="T6">
-        <v>0.1353525792711784</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1166,67 +1175,67 @@
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.0553803705163579</v>
+        <v>0.1021880544056771</v>
       </c>
       <c r="X6">
-        <v>0.1405241530862507</v>
+        <v>0.1040635995259769</v>
       </c>
       <c r="Y6">
-        <v>-0.08514378256989279</v>
+        <v>-0.001875545120299749</v>
       </c>
       <c r="Z6">
-        <v>1.001032753024491</v>
+        <v>0.5500631711939356</v>
       </c>
       <c r="AA6">
-        <v>-0.05626622689896112</v>
+        <v>-1.226202175429232</v>
       </c>
       <c r="AB6">
-        <v>0.08644991863203159</v>
+        <v>0.07530468254709954</v>
       </c>
       <c r="AC6">
-        <v>-0.1427161455309927</v>
+        <v>-1.301506857976332</v>
       </c>
       <c r="AD6">
-        <v>347.3</v>
+        <v>370.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>347.3</v>
+        <v>370.6</v>
       </c>
       <c r="AG6">
-        <v>347.3</v>
+        <v>370.6</v>
       </c>
       <c r="AH6">
-        <v>0.5379491945477075</v>
+        <v>0.4341103432119011</v>
       </c>
       <c r="AI6">
-        <v>0.2742419456727732</v>
+        <v>0.142046761211192</v>
       </c>
       <c r="AJ6">
-        <v>0.5379491945477075</v>
+        <v>0.4341103432119011</v>
       </c>
       <c r="AK6">
-        <v>0.2742419456727732</v>
+        <v>0.142046761211192</v>
       </c>
       <c r="AL6">
-        <v>15.2</v>
+        <v>16.6</v>
       </c>
       <c r="AM6">
-        <v>15.2</v>
+        <v>16.6</v>
       </c>
       <c r="AN6">
-        <v>-2.544322344322345</v>
+        <v>-0.2186817725851183</v>
       </c>
       <c r="AO6">
-        <v>-11.11184210526316</v>
+        <v>-104.0481927710843</v>
       </c>
       <c r="AP6">
-        <v>-2.544322344322345</v>
+        <v>-0.2186817725851183</v>
       </c>
       <c r="AQ6">
-        <v>-11.11184210526316</v>
+        <v>-104.0481927710843</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.035275</v>
+        <v>0.0111</v>
       </c>
       <c r="E2">
-        <v>0.10585</v>
-      </c>
-      <c r="F2">
-        <v>0.102</v>
+        <v>0.236</v>
       </c>
       <c r="G2">
-        <v>0.06105130221973214</v>
+        <v>0.1184661887095741</v>
       </c>
       <c r="H2">
-        <v>0.06105130221973214</v>
+        <v>0.1184661887095741</v>
       </c>
       <c r="I2">
-        <v>0.01902731823582122</v>
+        <v>0.1614997990716528</v>
       </c>
       <c r="J2">
-        <v>0.01749548871412529</v>
+        <v>0.1095978621343505</v>
       </c>
       <c r="K2">
-        <v>2001.9</v>
+        <v>447</v>
       </c>
       <c r="L2">
-        <v>0.03653442199912766</v>
+        <v>0.02603332498558558</v>
       </c>
       <c r="M2">
-        <v>400.508</v>
+        <v>85.6596</v>
       </c>
       <c r="N2">
-        <v>0.03249425986775385</v>
+        <v>0.06845101486335303</v>
       </c>
       <c r="O2">
-        <v>0.2000639392577052</v>
+        <v>0.1916322147651007</v>
       </c>
       <c r="P2">
-        <v>400.508</v>
+        <v>85.6596</v>
       </c>
       <c r="Q2">
-        <v>0.03249425986775385</v>
+        <v>0.06845101486335303</v>
       </c>
       <c r="R2">
-        <v>0.2000639392577052</v>
+        <v>0.1916322147651007</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.0001711898097440266</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.0896642226042354</v>
+        <v>0.04181908334814621</v>
       </c>
       <c r="X2">
-        <v>0.1209033755528086</v>
+        <v>0.2847094860448345</v>
       </c>
       <c r="Y2">
-        <v>-0.03123915294857321</v>
+        <v>-0.2428904026966883</v>
       </c>
       <c r="Z2">
-        <v>1.237424463222829</v>
+        <v>0.9376938704181047</v>
       </c>
       <c r="AA2">
-        <v>0.05561058891811879</v>
+        <v>0.1027692435343089</v>
       </c>
       <c r="AB2">
-        <v>0.07447550749894481</v>
+        <v>0.07494819498527808</v>
       </c>
       <c r="AC2">
-        <v>-0.01764489664558282</v>
+        <v>0.02782104854903086</v>
       </c>
       <c r="AD2">
-        <v>26123.2</v>
+        <v>8590.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26123.2</v>
+        <v>8590.5</v>
       </c>
       <c r="AG2">
-        <v>26121.09</v>
+        <v>8590.5</v>
       </c>
       <c r="AH2">
-        <v>0.6794299937319078</v>
+        <v>0.8728497546205509</v>
       </c>
       <c r="AI2">
-        <v>0.3415435826566273</v>
+        <v>0.4526676327229614</v>
       </c>
       <c r="AJ2">
-        <v>0.6794124004235487</v>
+        <v>0.8728497546205509</v>
       </c>
       <c r="AK2">
-        <v>0.3415254174130686</v>
+        <v>0.4526676327229614</v>
       </c>
       <c r="AL2">
-        <v>932.1</v>
+        <v>380.4</v>
       </c>
       <c r="AM2">
-        <v>932.1</v>
+        <v>380.4</v>
       </c>
       <c r="AN2">
-        <v>16.39771514656958</v>
+        <v>2.998220019544884</v>
       </c>
       <c r="AO2">
-        <v>1.118549511854951</v>
+        <v>7.28969505783386</v>
       </c>
       <c r="AP2">
-        <v>16.39639068482832</v>
+        <v>2.998220019544884</v>
       </c>
       <c r="AQ2">
-        <v>1.118549511854951</v>
+        <v>7.28969505783386</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tong Yang Life Insurance Co., Ltd. (KOSE:A082640)</t>
+          <t>Hanwha Life Insurance Co., Ltd. (KOSE:A088350)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,50 +722,53 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.12</v>
+        <v>0.0111</v>
       </c>
       <c r="E3">
-        <v>0.154</v>
+        <v>0.236</v>
       </c>
       <c r="G3">
-        <v>0.07073361738276325</v>
+        <v>0.1184661887095741</v>
       </c>
       <c r="H3">
-        <v>0.07073361738276325</v>
+        <v>0.1184661887095741</v>
       </c>
       <c r="I3">
-        <v>0.1387063804935027</v>
+        <v>0.1614997990716528</v>
       </c>
       <c r="J3">
-        <v>0.1124059126340587</v>
+        <v>0.1095978621343505</v>
       </c>
       <c r="K3">
-        <v>98.3</v>
+        <v>447</v>
       </c>
       <c r="L3">
-        <v>0.01304769110288164</v>
+        <v>0.02603332498558558</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>85.6596</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06845101486335303</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1916322147651007</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>85.6596</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06845101486335303</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1916322147651007</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -776,466 +776,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.0771403908027937</v>
+        <v>0.04181908334814621</v>
       </c>
       <c r="X3">
-        <v>0.08862582417263795</v>
+        <v>0.2847094860448345</v>
       </c>
       <c r="Y3">
-        <v>-0.01148543336984426</v>
+        <v>-0.2428904026966883</v>
       </c>
       <c r="Z3">
-        <v>5.079490291262135</v>
+        <v>0.9376938704181047</v>
       </c>
       <c r="AA3">
-        <v>0.5709647419051608</v>
+        <v>0.1027692435343089</v>
       </c>
       <c r="AB3">
-        <v>0.07781499524640231</v>
+        <v>0.07494819498527808</v>
       </c>
       <c r="AC3">
-        <v>0.4931497466587584</v>
+        <v>0.02782104854903086</v>
       </c>
       <c r="AD3">
-        <v>148.3</v>
+        <v>8590.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>148.3</v>
+        <v>8590.5</v>
       </c>
       <c r="AG3">
-        <v>148.3</v>
+        <v>8590.5</v>
       </c>
       <c r="AH3">
-        <v>0.2127690100430416</v>
+        <v>0.8728497546205509</v>
       </c>
       <c r="AI3">
-        <v>0.05824594477828836</v>
+        <v>0.4526676327229614</v>
       </c>
       <c r="AJ3">
-        <v>0.2127690100430416</v>
+        <v>0.8728497546205509</v>
       </c>
       <c r="AK3">
-        <v>0.05824594477828836</v>
+        <v>0.4526676327229614</v>
       </c>
       <c r="AL3">
-        <v>46.5</v>
+        <v>380.4</v>
       </c>
       <c r="AM3">
-        <v>46.5</v>
+        <v>380.4</v>
       </c>
       <c r="AN3">
-        <v>0.1396158915458482</v>
+        <v>2.998220019544884</v>
       </c>
       <c r="AO3">
-        <v>22.47311827956989</v>
+        <v>7.28969505783386</v>
       </c>
       <c r="AP3">
-        <v>0.1396158915458482</v>
+        <v>2.998220019544884</v>
       </c>
       <c r="AQ3">
-        <v>22.47311827956989</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hanwha Life Insurance Co., Ltd. (KOSE:A088350)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0614</v>
-      </c>
-      <c r="E4">
-        <v>-0.0294</v>
-      </c>
-      <c r="G4">
-        <v>0.05474449295938139</v>
-      </c>
-      <c r="H4">
-        <v>0.05474449295938139</v>
-      </c>
-      <c r="I4">
-        <v>0.04313216004571715</v>
-      </c>
-      <c r="J4">
-        <v>0.04313216004571715</v>
-      </c>
-      <c r="K4">
-        <v>187.7</v>
-      </c>
-      <c r="L4">
-        <v>0.00837998803496647</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0.04272803842564138</v>
-      </c>
-      <c r="X4">
-        <v>0.226107129230268</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1833790908046266</v>
-      </c>
-      <c r="Z4">
-        <v>2.018892243904638</v>
-      </c>
-      <c r="AA4">
-        <v>0.08707918337915184</v>
-      </c>
-      <c r="AB4">
-        <v>0.07364633245079008</v>
-      </c>
-      <c r="AC4">
-        <v>0.01343285092836176</v>
-      </c>
-      <c r="AD4">
-        <v>7757.1</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>7757.1</v>
-      </c>
-      <c r="AG4">
-        <v>7757.1</v>
-      </c>
-      <c r="AH4">
-        <v>0.8244077667839265</v>
-      </c>
-      <c r="AI4">
-        <v>0.3820102432778489</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8244077667839265</v>
-      </c>
-      <c r="AK4">
-        <v>0.3820102432778489</v>
-      </c>
-      <c r="AL4">
-        <v>129.1</v>
-      </c>
-      <c r="AM4">
-        <v>129.1</v>
-      </c>
-      <c r="AN4">
-        <v>6.672774193548388</v>
-      </c>
-      <c r="AO4">
-        <v>7.483346243222309</v>
-      </c>
-      <c r="AP4">
-        <v>6.672774193548388</v>
-      </c>
-      <c r="AQ4">
-        <v>7.483346243222309</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Samsung Life Insurance Co., Ltd. (KOSE:A032830)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.00915</v>
-      </c>
-      <c r="E5">
-        <v>0.0617</v>
-      </c>
-      <c r="F5">
-        <v>0.102</v>
-      </c>
-      <c r="G5">
-        <v>0.06427264977778514</v>
-      </c>
-      <c r="H5">
-        <v>0.06427264977778514</v>
-      </c>
-      <c r="I5">
-        <v>0.03139560867010403</v>
-      </c>
-      <c r="J5">
-        <v>0.03040732644102825</v>
-      </c>
-      <c r="K5">
-        <v>1629.5</v>
-      </c>
-      <c r="L5">
-        <v>0.06743000438636421</v>
-      </c>
-      <c r="M5">
-        <v>400.508</v>
-      </c>
-      <c r="N5">
-        <v>0.0415400093346471</v>
-      </c>
-      <c r="O5">
-        <v>0.2457858238723535</v>
-      </c>
-      <c r="P5">
-        <v>400.508</v>
-      </c>
-      <c r="Q5">
-        <v>0.0415400093346471</v>
-      </c>
-      <c r="R5">
-        <v>0.2457858238723535</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2.11</v>
-      </c>
-      <c r="V5">
-        <v>0.0002188456153088212</v>
-      </c>
-      <c r="W5">
-        <v>0.1156157541098758</v>
-      </c>
-      <c r="X5">
-        <v>0.1377431515796403</v>
-      </c>
-      <c r="Y5">
-        <v>-0.02212739746976458</v>
-      </c>
-      <c r="Z5">
-        <v>0.7939532107140874</v>
-      </c>
-      <c r="AA5">
-        <v>0.02414199445708574</v>
-      </c>
-      <c r="AB5">
-        <v>0.07286463867661315</v>
-      </c>
-      <c r="AC5">
-        <v>-0.04872264421952741</v>
-      </c>
-      <c r="AD5">
-        <v>17847.2</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>17847.2</v>
-      </c>
-      <c r="AG5">
-        <v>17845.09</v>
-      </c>
-      <c r="AH5">
-        <v>0.6492558760508864</v>
-      </c>
-      <c r="AI5">
-        <v>0.3497763823724243</v>
-      </c>
-      <c r="AJ5">
-        <v>0.649228951281334</v>
-      </c>
-      <c r="AK5">
-        <v>0.3497494928216949</v>
-      </c>
-      <c r="AL5">
-        <v>739.9</v>
-      </c>
-      <c r="AM5">
-        <v>739.9</v>
-      </c>
-      <c r="AN5">
-        <v>16.78788448875929</v>
-      </c>
-      <c r="AO5">
-        <v>1.025408839032302</v>
-      </c>
-      <c r="AP5">
-        <v>16.78589972721287</v>
-      </c>
-      <c r="AQ5">
-        <v>1.025408839032302</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MIRAE ASSET Life Insurance Co., Ltd. (KOSE:A085620)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.238</v>
-      </c>
-      <c r="E6">
-        <v>0.15</v>
-      </c>
-      <c r="G6">
-        <v>0.04737295434969854</v>
-      </c>
-      <c r="H6">
-        <v>0.04737295434969854</v>
-      </c>
-      <c r="I6">
-        <v>-2.479471719781797</v>
-      </c>
-      <c r="J6">
-        <v>-2.229202461905799</v>
-      </c>
-      <c r="K6">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="L6">
-        <v>0.124031007751938</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0.1021880544056771</v>
-      </c>
-      <c r="X6">
-        <v>0.1040635995259769</v>
-      </c>
-      <c r="Y6">
-        <v>-0.001875545120299749</v>
-      </c>
-      <c r="Z6">
-        <v>0.5500631711939356</v>
-      </c>
-      <c r="AA6">
-        <v>-1.226202175429232</v>
-      </c>
-      <c r="AB6">
-        <v>0.07530468254709954</v>
-      </c>
-      <c r="AC6">
-        <v>-1.301506857976332</v>
-      </c>
-      <c r="AD6">
-        <v>370.6</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>370.6</v>
-      </c>
-      <c r="AG6">
-        <v>370.6</v>
-      </c>
-      <c r="AH6">
-        <v>0.4341103432119011</v>
-      </c>
-      <c r="AI6">
-        <v>0.142046761211192</v>
-      </c>
-      <c r="AJ6">
-        <v>0.4341103432119011</v>
-      </c>
-      <c r="AK6">
-        <v>0.142046761211192</v>
-      </c>
-      <c r="AL6">
-        <v>16.6</v>
-      </c>
-      <c r="AM6">
-        <v>16.6</v>
-      </c>
-      <c r="AN6">
-        <v>-0.2186817725851183</v>
-      </c>
-      <c r="AO6">
-        <v>-104.0481927710843</v>
-      </c>
-      <c r="AP6">
-        <v>-0.2186817725851183</v>
-      </c>
-      <c r="AQ6">
-        <v>-104.0481927710843</v>
+        <v>7.28969505783386</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0111</v>
+        <v>0.004755000000000001</v>
       </c>
       <c r="E2">
-        <v>0.236</v>
+        <v>0.212</v>
+      </c>
+      <c r="F2">
+        <v>0.09269999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1184661887095741</v>
+        <v>0.1327694853935103</v>
       </c>
       <c r="H2">
-        <v>0.1184661887095741</v>
+        <v>0.1327694853935103</v>
       </c>
       <c r="I2">
-        <v>0.1614997990716528</v>
+        <v>0.176420811088228</v>
       </c>
       <c r="J2">
-        <v>0.1095978621343505</v>
+        <v>0.1439182589552961</v>
       </c>
       <c r="K2">
-        <v>447</v>
+        <v>2576.5</v>
       </c>
       <c r="L2">
-        <v>0.02603332498558558</v>
+        <v>0.05663023194986911</v>
       </c>
       <c r="M2">
-        <v>85.6596</v>
+        <v>639.6811</v>
       </c>
       <c r="N2">
-        <v>0.06845101486335303</v>
+        <v>0.04663792386937788</v>
       </c>
       <c r="O2">
-        <v>0.1916322147651007</v>
+        <v>0.2482752183194256</v>
       </c>
       <c r="P2">
-        <v>85.6596</v>
+        <v>639.6811</v>
       </c>
       <c r="Q2">
-        <v>0.06845101486335303</v>
+        <v>0.04663792386937788</v>
       </c>
       <c r="R2">
-        <v>0.1916322147651007</v>
+        <v>0.2482752183194256</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.0001618559482060966</v>
       </c>
       <c r="W2">
-        <v>0.04181908334814621</v>
+        <v>0.0507022307391291</v>
       </c>
       <c r="X2">
-        <v>0.2847094860448345</v>
+        <v>0.1143526082054153</v>
       </c>
       <c r="Y2">
-        <v>-0.2428904026966883</v>
+        <v>-0.06365037746628618</v>
       </c>
       <c r="Z2">
-        <v>0.9376938704181047</v>
+        <v>0.6234613672219781</v>
       </c>
       <c r="AA2">
-        <v>0.1027692435343089</v>
+        <v>0.1225777534984028</v>
       </c>
       <c r="AB2">
-        <v>0.07494819498527808</v>
+        <v>0.07978152543296503</v>
       </c>
       <c r="AC2">
-        <v>0.02782104854903086</v>
+        <v>0.04449684249003544</v>
       </c>
       <c r="AD2">
-        <v>8590.5</v>
+        <v>26688.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8590.5</v>
+        <v>26688.6</v>
       </c>
       <c r="AG2">
-        <v>8590.5</v>
+        <v>26686.38</v>
       </c>
       <c r="AH2">
-        <v>0.8728497546205509</v>
+        <v>0.6605353364105483</v>
       </c>
       <c r="AI2">
-        <v>0.4526676327229614</v>
+        <v>0.3962860893167902</v>
       </c>
       <c r="AJ2">
-        <v>0.8728497546205509</v>
+        <v>0.6605166837119093</v>
       </c>
       <c r="AK2">
-        <v>0.4526676327229614</v>
+        <v>0.3962661880139426</v>
       </c>
       <c r="AL2">
-        <v>380.4</v>
+        <v>1922.6</v>
       </c>
       <c r="AM2">
-        <v>380.4</v>
+        <v>1922.6</v>
       </c>
       <c r="AN2">
-        <v>2.998220019544884</v>
+        <v>3.184113197642511</v>
       </c>
       <c r="AO2">
-        <v>7.28969505783386</v>
+        <v>4.174867367107042</v>
       </c>
       <c r="AP2">
-        <v>2.998220019544884</v>
+        <v>3.183848338065809</v>
       </c>
       <c r="AQ2">
-        <v>7.28969505783386</v>
+        <v>4.174867367107042</v>
       </c>
     </row>
     <row r="3">
@@ -713,130 +716,532 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Tong Yang Life Insurance Co., Ltd. (KOSE:A082640)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.115</v>
+      </c>
+      <c r="E3">
+        <v>0.202</v>
+      </c>
+      <c r="G3">
+        <v>0.1927043052333075</v>
+      </c>
+      <c r="H3">
+        <v>0.1927043052333075</v>
+      </c>
+      <c r="I3">
+        <v>0.2373463951190169</v>
+      </c>
+      <c r="J3">
+        <v>0.1870227153521599</v>
+      </c>
+      <c r="K3">
+        <v>251.6</v>
+      </c>
+      <c r="L3">
+        <v>0.1081034630918622</v>
+      </c>
+      <c r="M3">
+        <v>47.5495</v>
+      </c>
+      <c r="N3">
+        <v>0.1003154008438819</v>
+      </c>
+      <c r="O3">
+        <v>0.1889884737678856</v>
+      </c>
+      <c r="P3">
+        <v>47.5495</v>
+      </c>
+      <c r="Q3">
+        <v>0.1003154008438819</v>
+      </c>
+      <c r="R3">
+        <v>0.1889884737678856</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.1049295187254984</v>
+      </c>
+      <c r="X3">
+        <v>0.08463714224288127</v>
+      </c>
+      <c r="Y3">
+        <v>0.0202923764826171</v>
+      </c>
+      <c r="Z3">
+        <v>0.914103923647932</v>
+      </c>
+      <c r="AA3">
+        <v>0.1709581979146997</v>
+      </c>
+      <c r="AB3">
+        <v>0.08463714224288127</v>
+      </c>
+      <c r="AC3">
+        <v>0.08632105567181841</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>100</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>5.524</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>5.524</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MIRAE ASSET Life Insurance Co., Ltd. (KOSE:A085620)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0796</v>
+      </c>
+      <c r="E4">
+        <v>-0.213</v>
+      </c>
+      <c r="G4">
+        <v>0.1081743791520543</v>
+      </c>
+      <c r="H4">
+        <v>0.1081743791520543</v>
+      </c>
+      <c r="I4">
+        <v>0.1059219342514185</v>
+      </c>
+      <c r="J4">
+        <v>0.1059219342514185</v>
+      </c>
+      <c r="K4">
+        <v>-16.2</v>
+      </c>
+      <c r="L4">
+        <v>-0.004618937644341801</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>-0.0075</v>
+      </c>
+      <c r="X4">
+        <v>0.09890384755659276</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1064038475565928</v>
+      </c>
+      <c r="Z4">
+        <v>1.344256640220766</v>
+      </c>
+      <c r="AA4">
+        <v>0.1423862634624967</v>
+      </c>
+      <c r="AB4">
+        <v>0.08122863208186976</v>
+      </c>
+      <c r="AC4">
+        <v>0.06115763138062691</v>
+      </c>
+      <c r="AD4">
+        <v>228</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>228</v>
+      </c>
+      <c r="AG4">
+        <v>228</v>
+      </c>
+      <c r="AH4">
+        <v>0.3287671232876712</v>
+      </c>
+      <c r="AI4">
+        <v>0.1105615362234507</v>
+      </c>
+      <c r="AJ4">
+        <v>0.3287671232876712</v>
+      </c>
+      <c r="AK4">
+        <v>0.1105615362234507</v>
+      </c>
+      <c r="AL4">
+        <v>11.1</v>
+      </c>
+      <c r="AM4">
+        <v>11.1</v>
+      </c>
+      <c r="AN4">
+        <v>0.5741626794258373</v>
+      </c>
+      <c r="AO4">
+        <v>33.46846846846847</v>
+      </c>
+      <c r="AP4">
+        <v>0.5741626794258373</v>
+      </c>
+      <c r="AQ4">
+        <v>33.46846846846847</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Hanwha Life Insurance Co., Ltd. (KOSE:A088350)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>0.0111</v>
       </c>
-      <c r="E3">
+      <c r="E5">
         <v>0.236</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>0.1184661887095741</v>
       </c>
-      <c r="H3">
+      <c r="H5">
         <v>0.1184661887095741</v>
       </c>
-      <c r="I3">
+      <c r="I5">
         <v>0.1614997990716528</v>
       </c>
-      <c r="J3">
+      <c r="J5">
         <v>0.1095978621343505</v>
       </c>
-      <c r="K3">
+      <c r="K5">
         <v>447</v>
       </c>
-      <c r="L3">
+      <c r="L5">
         <v>0.02603332498558558</v>
       </c>
-      <c r="M3">
+      <c r="M5">
         <v>85.6596</v>
       </c>
-      <c r="N3">
+      <c r="N5">
         <v>0.06845101486335303</v>
       </c>
-      <c r="O3">
+      <c r="O5">
         <v>0.1916322147651007</v>
       </c>
-      <c r="P3">
+      <c r="P5">
         <v>85.6596</v>
       </c>
-      <c r="Q3">
+      <c r="Q5">
         <v>0.06845101486335303</v>
       </c>
-      <c r="R3">
+      <c r="R5">
         <v>0.1916322147651007</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
         <v>0.04181908334814621</v>
       </c>
-      <c r="X3">
-        <v>0.2847094860448345</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2428904026966883</v>
-      </c>
-      <c r="Z3">
+      <c r="X5">
+        <v>0.284591475651946</v>
+      </c>
+      <c r="Y5">
+        <v>-0.2427723923037998</v>
+      </c>
+      <c r="Z5">
         <v>0.9376938704181047</v>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <v>0.1027692435343089</v>
       </c>
-      <c r="AB3">
-        <v>0.07494819498527808</v>
-      </c>
-      <c r="AC3">
-        <v>0.02782104854903086</v>
-      </c>
-      <c r="AD3">
+      <c r="AB5">
+        <v>0.07493318993486497</v>
+      </c>
+      <c r="AC5">
+        <v>0.02783605359944397</v>
+      </c>
+      <c r="AD5">
         <v>8590.5</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>8590.5</v>
       </c>
-      <c r="AG3">
+      <c r="AG5">
         <v>8590.5</v>
       </c>
-      <c r="AH3">
+      <c r="AH5">
         <v>0.8728497546205509</v>
       </c>
-      <c r="AI3">
+      <c r="AI5">
         <v>0.4526676327229614</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ5">
         <v>0.8728497546205509</v>
       </c>
-      <c r="AK3">
+      <c r="AK5">
         <v>0.4526676327229614</v>
       </c>
-      <c r="AL3">
+      <c r="AL5">
         <v>380.4</v>
       </c>
-      <c r="AM3">
+      <c r="AM5">
         <v>380.4</v>
       </c>
-      <c r="AN3">
+      <c r="AN5">
         <v>2.998220019544884</v>
       </c>
-      <c r="AO3">
+      <c r="AO5">
         <v>7.28969505783386</v>
       </c>
-      <c r="AP3">
+      <c r="AP5">
         <v>2.998220019544884</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ5">
         <v>7.28969505783386</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Samsung Life Insurance Co., Ltd. (KOSE:A032830)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.00159</v>
+      </c>
+      <c r="E6">
+        <v>0.222</v>
+      </c>
+      <c r="F6">
+        <v>0.09269999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.1413219870264406</v>
+      </c>
+      <c r="H6">
+        <v>0.1413219870264406</v>
+      </c>
+      <c r="I6">
+        <v>0.1925004112591644</v>
+      </c>
+      <c r="J6">
+        <v>0.1533205230460821</v>
+      </c>
+      <c r="K6">
+        <v>1894.1</v>
+      </c>
+      <c r="L6">
+        <v>0.08421253873616723</v>
+      </c>
+      <c r="M6">
+        <v>506.472</v>
+      </c>
+      <c r="N6">
+        <v>0.04394550976138829</v>
+      </c>
+      <c r="O6">
+        <v>0.267394540942928</v>
+      </c>
+      <c r="P6">
+        <v>506.472</v>
+      </c>
+      <c r="Q6">
+        <v>0.04394550976138829</v>
+      </c>
+      <c r="R6">
+        <v>0.267394540942928</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>2.22</v>
+      </c>
+      <c r="V6">
+        <v>0.0001926247288503254</v>
+      </c>
+      <c r="W6">
+        <v>0.05958537813011199</v>
+      </c>
+      <c r="X6">
+        <v>0.1298013688542378</v>
+      </c>
+      <c r="Y6">
+        <v>-0.07021599072412582</v>
+      </c>
+      <c r="Z6">
+        <v>0.4543057334438335</v>
+      </c>
+      <c r="AA6">
+        <v>0.06965439267444248</v>
+      </c>
+      <c r="AB6">
+        <v>0.07833441878406031</v>
+      </c>
+      <c r="AC6">
+        <v>-0.008680026109617822</v>
+      </c>
+      <c r="AD6">
+        <v>17870.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>17870.1</v>
+      </c>
+      <c r="AG6">
+        <v>17867.88</v>
+      </c>
+      <c r="AH6">
+        <v>0.6079278519208984</v>
+      </c>
+      <c r="AI6">
+        <v>0.3994818166373074</v>
+      </c>
+      <c r="AJ6">
+        <v>0.6078982393014907</v>
+      </c>
+      <c r="AK6">
+        <v>0.3994520129002315</v>
+      </c>
+      <c r="AL6">
+        <v>1431.1</v>
+      </c>
+      <c r="AM6">
+        <v>1431.1</v>
+      </c>
+      <c r="AN6">
+        <v>3.929912913441238</v>
+      </c>
+      <c r="AO6">
+        <v>3.025434980085249</v>
+      </c>
+      <c r="AP6">
+        <v>3.929424700914848</v>
+      </c>
+      <c r="AQ6">
+        <v>3.025434980085249</v>
       </c>
     </row>
   </sheetData>
